--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2017-2018.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2017-2018.xlsx
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 1</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2017-2018.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2017-2018.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
